--- a/sourcedata/Dim_SalesRep.xlsx
+++ b/sourcedata/Dim_SalesRep.xlsx
@@ -433,7 +433,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -443,7 +443,7 @@
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="29" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="39" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
   </cols>
@@ -538,17 +538,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jennifer Allen</t>
+          <t>Susan Garcia</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>jennifer.allen@pharmacore.com</t>
+          <t>susan.garcia@pharmacore.com</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -620,17 +620,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Daniel Thompson</t>
+          <t>Barbara Smith</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>daniel.thompson@pharmacore.com</t>
+          <t>barbara.smith@pharmacore.com</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Martinez</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Joseph Johnson</t>
+          <t>Daniel Martinez</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>joseph.johnson@pharmacore.com</t>
+          <t>daniel.martinez@pharmacore.com</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>John</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Karen Davis</t>
+          <t>John Wilson</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>karen.davis@pharmacore.com</t>
+          <t>john.wilson@pharmacore.com</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hernandez</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ashley Hernandez</t>
+          <t>Mary Johnson</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ashley.hernandez@pharmacore.com</t>
+          <t>mary.johnson@pharmacore.com</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -948,17 +948,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Patricia</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Patricia Harris</t>
+          <t>Karen Taylor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>patricia.harris@pharmacore.com</t>
+          <t>karen.taylor@pharmacore.com</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1030,17 +1030,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>John Allen</t>
+          <t>Daniel Jones</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>john.allen@pharmacore.com</t>
+          <t>daniel.jones@pharmacore.com</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1112,17 +1112,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Christopher</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lewis</t>
+          <t>Hernandez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Joseph Lewis</t>
+          <t>Christopher Hernandez</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>joseph.lewis@pharmacore.com</t>
+          <t>christopher.hernandez@pharmacore.com</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Martinez</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thomas Martinez</t>
+          <t>Matthew Martin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>thomas.martinez@pharmacore.com</t>
+          <t>matthew.martin@pharmacore.com</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Hernandez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lisa Anderson</t>
+          <t>Patricia Hernandez</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>lisa.anderson@pharmacore.com</t>
+          <t>patricia.hernandez@pharmacore.com</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
